--- a/schema/excel/chemrof.xlsx
+++ b/schema/excel/chemrof.xlsx
@@ -1463,7 +1463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1584,65 +1584,70 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -1659,7 +1664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1780,65 +1785,70 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -1855,7 +1865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1951,65 +1961,70 @@
       </c>
       <c r="S1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -2026,7 +2041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2147,65 +2162,70 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -2258,7 +2278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2379,65 +2399,70 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -2454,7 +2479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV1"/>
+  <dimension ref="A1:AW1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2635,65 +2660,70 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -2710,7 +2740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM1"/>
+  <dimension ref="A1:AN1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2846,65 +2876,70 @@
       </c>
       <c r="AA1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -2932,7 +2967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3043,65 +3078,70 @@
       </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -3185,7 +3225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN1"/>
+  <dimension ref="A1:AO1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3326,65 +3366,70 @@
       </c>
       <c r="AB1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -3401,7 +3446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3507,65 +3552,70 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -3582,7 +3632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN1"/>
+  <dimension ref="A1:AO1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3723,65 +3773,70 @@
       </c>
       <c r="AB1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -3798,7 +3853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN1"/>
+  <dimension ref="A1:AO1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3939,65 +3994,70 @@
       </c>
       <c r="AB1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -4014,7 +4074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1"/>
+  <dimension ref="A1:AE1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4105,65 +4165,70 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -4216,7 +4281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1"/>
+  <dimension ref="A1:AE1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4307,65 +4372,70 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -4382,7 +4452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1"/>
+  <dimension ref="A1:AE1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4473,65 +4543,70 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -4548,7 +4623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1"/>
+  <dimension ref="A1:AE1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4639,65 +4714,70 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -4714,7 +4794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1"/>
+  <dimension ref="A1:AE1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4805,65 +4885,70 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -4880,7 +4965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4991,65 +5076,70 @@
       </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -5066,7 +5156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5187,65 +5277,70 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -5262,7 +5357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK1"/>
+  <dimension ref="A1:AL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5388,65 +5483,70 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -5463,7 +5563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1"/>
+  <dimension ref="A1:AE1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5554,65 +5654,70 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -5629,7 +5734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5725,65 +5830,70 @@
       </c>
       <c r="S1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -5800,7 +5910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5896,65 +6006,70 @@
       </c>
       <c r="S1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -6022,7 +6137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6118,65 +6233,70 @@
       </c>
       <c r="S1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -6193,7 +6313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6289,65 +6409,70 @@
       </c>
       <c r="S1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -6364,7 +6489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1"/>
+  <dimension ref="A1:AE1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6455,65 +6580,70 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -6530,7 +6660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6651,65 +6781,70 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -6726,7 +6861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6847,65 +6982,70 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -6922,7 +7062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN1"/>
+  <dimension ref="A1:AO1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7058,70 +7198,75 @@
       </c>
       <c r="AA1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>elemental_charge</t>
         </is>
@@ -7143,7 +7288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN1"/>
+  <dimension ref="A1:AO1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7279,70 +7424,75 @@
       </c>
       <c r="AA1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>elemental_charge</t>
         </is>
@@ -7364,7 +7514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN1"/>
+  <dimension ref="A1:AO1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7500,70 +7650,75 @@
       </c>
       <c r="AA1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>elemental_charge</t>
         </is>
@@ -7585,7 +7740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL1"/>
+  <dimension ref="A1:AM1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7711,70 +7866,75 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>elemental_charge</t>
         </is>
@@ -7796,7 +7956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL1"/>
+  <dimension ref="A1:AM1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7922,70 +8082,75 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>elemental_charge</t>
         </is>
@@ -8058,7 +8223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL1"/>
+  <dimension ref="A1:AM1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8184,70 +8349,75 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>elemental_charge</t>
         </is>
@@ -8269,7 +8439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8395,60 +8565,65 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -8470,7 +8645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI1"/>
+  <dimension ref="A1:AJ1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8591,60 +8766,65 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -8661,7 +8841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI1"/>
+  <dimension ref="A1:AJ1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8782,60 +8962,65 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -8852,7 +9037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI1"/>
+  <dimension ref="A1:AJ1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8973,60 +9158,65 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -9043,7 +9233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ1"/>
+  <dimension ref="A1:AR1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9204,60 +9394,65 @@
       </c>
       <c r="AF1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -9274,7 +9469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ1"/>
+  <dimension ref="A1:AR1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9435,60 +9630,65 @@
       </c>
       <c r="AF1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -9505,7 +9705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9631,60 +9831,65 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -9701,7 +9906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9827,60 +10032,65 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -9897,7 +10107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10023,60 +10233,65 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -10144,7 +10359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10270,60 +10485,65 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -10945,7 +11165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11041,65 +11261,70 @@
       </c>
       <c r="S1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -11116,7 +11341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11237,65 +11462,70 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -11312,7 +11542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK1"/>
+  <dimension ref="A1:AL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11438,65 +11668,70 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -11513,7 +11748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO1"/>
+  <dimension ref="A1:AP1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11659,65 +11894,70 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -11790,7 +12030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11901,65 +12141,70 @@
       </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -11976,7 +12221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12097,65 +12342,70 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>molecular_formula</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>classified_by</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
